--- a/data/trans_orig/IP07A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A07-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53657</t>
+          <t>53356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69042</t>
+          <t>69301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>35118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64998</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45178</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66694</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95678</t>
+          <t>95004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>123975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114637</t>
+          <t>114134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136808</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144873</t>
+          <t>144357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167827</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>266637</t>
+          <t>267240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298218</t>
+          <t>300048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>46609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44535</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69670</t>
+          <t>70627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>88261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86350</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67067</t>
+          <t>68287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91880</t>
+          <t>91605</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141591</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175819</t>
+          <t>175983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178312</t>
+          <t>178514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>207167</t>
+          <t>207503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>216336</t>
+          <t>216933</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>244543</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>403622</t>
+          <t>403206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>444268</t>
+          <t>444202</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27885</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33733</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58747</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74980</t>
+          <t>74768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43773</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71388</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70316</t>
+          <t>70326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>40179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60506</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93719</t>
+          <t>93993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125290</t>
+          <t>123629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101678</t>
+          <t>100204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123787</t>
+          <t>124058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129033</t>
+          <t>128460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151971</t>
+          <t>152794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235604</t>
+          <t>236123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270542</t>
+          <t>270110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29001</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>41800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27540</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>39736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59882</t>
+          <t>60580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78972</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>63601</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>103061</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>100982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139701</t>
+          <t>140364</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175810</t>
+          <t>177557</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172597</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202895</t>
+          <t>202068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188719</t>
+          <t>189451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>216150</t>
+          <t>217487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>370177</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>411319</t>
+          <t>409532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23485</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26751</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>34493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28247</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63870</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>44799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>66677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92574</t>
+          <t>93264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122889</t>
+          <t>124826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>145467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170613</t>
+          <t>170965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145280</t>
+          <t>145864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170518</t>
+          <t>170323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297462</t>
+          <t>298676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332775</t>
+          <t>336102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,47 +8142,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5108</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23743</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>43955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37431</t>
+          <t>37761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52073</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55839</t>
+          <t>56590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84862</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105168</t>
+          <t>105860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>72539</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65392</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91831</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95342</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142948</t>
+          <t>144112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179003</t>
+          <t>181989</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205625</t>
+          <t>205433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>235299</t>
+          <t>234217</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>214060</t>
+          <t>214285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>244691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>429540</t>
+          <t>427074</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>471547</t>
+          <t>472398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
